--- a/dolbabot/static/table.xlsx
+++ b/dolbabot/static/table.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Apsil\PycharmProjects\DolbaBot\dolbabot\static\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70A7B71C-1068-42E2-95E0-4A0C92040EF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0F62EE7-E330-4B06-9928-31C0CB723646}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="41">
   <si>
     <t>Калининград</t>
   </si>
@@ -232,7 +232,18 @@
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="1">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -709,18 +720,18 @@
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" s="4">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="B25" t="s">
-        <v>12</v>
+        <v>30</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" s="4">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="B26" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
@@ -728,7 +739,7 @@
         <v>1</v>
       </c>
       <c r="B27" t="s">
-        <v>16</v>
+        <v>32</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
@@ -736,7 +747,7 @@
         <v>1</v>
       </c>
       <c r="B28" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
@@ -744,15 +755,15 @@
         <v>1</v>
       </c>
       <c r="B29" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" s="4">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="B30" t="s">
-        <v>13</v>
+        <v>35</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
@@ -760,137 +771,97 @@
         <v>1</v>
       </c>
       <c r="B31" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A32" s="4">
-        <v>0.9</v>
-      </c>
-      <c r="B32" t="s">
-        <v>14</v>
+      <c r="A32" s="5">
+        <v>1.2</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>0</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A33" s="4">
-        <v>1</v>
-      </c>
-      <c r="B33" t="s">
-        <v>34</v>
+      <c r="A33" s="5">
+        <v>1</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>1</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A34" s="4">
-        <v>1.4</v>
-      </c>
-      <c r="B34" t="s">
-        <v>35</v>
+      <c r="A34" s="5">
+        <v>1.2</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A35" s="4">
-        <v>1</v>
-      </c>
-      <c r="B35" t="s">
-        <v>36</v>
-      </c>
+      <c r="A35" s="5">
+        <v>1.2</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C35" s="1"/>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" s="5">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>0</v>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="C36" s="2"/>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" s="5">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="C37" s="1"/>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" s="5">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C38" s="2"/>
+        <v>9</v>
+      </c>
+      <c r="C38" s="1"/>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" s="5">
-        <v>0.7</v>
+        <v>0.55000000000000004</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="C39" s="1"/>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" s="5">
-        <v>1.2</v>
+        <v>0.45</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>5</v>
+        <v>37</v>
       </c>
       <c r="C40" s="1"/>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A41" s="5">
-        <v>1.2</v>
-      </c>
-      <c r="B41" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C41" s="1"/>
-    </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A42" s="5">
-        <v>1.4</v>
-      </c>
-      <c r="B42" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C42" s="1"/>
-    </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A43" s="5">
-        <v>1.2</v>
-      </c>
-      <c r="B43" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="C43" s="1"/>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A44" s="5">
-        <v>1</v>
-      </c>
-      <c r="B44" s="3" t="s">
-        <v>9</v>
-      </c>
       <c r="C44" s="1"/>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A45" s="5">
-        <v>0.55000000000000004</v>
-      </c>
-      <c r="B45" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="C45" s="1"/>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A46" s="5">
-        <v>0.45</v>
-      </c>
-      <c r="B46" s="3" t="s">
-        <v>37</v>
-      </c>
       <c r="C46" s="1"/>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
@@ -901,6 +872,9 @@
       <c r="A48" s="7"/>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="B46:B1048576 B1:B40">
+    <cfRule type="duplicateValues" dxfId="0" priority="3"/>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/dolbabot/static/table.xlsx
+++ b/dolbabot/static/table.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Apsil\PycharmProjects\DolbaBot\dolbabot\static\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Apsil\Downloads\Telegram Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0F62EE7-E330-4B06-9928-31C0CB723646}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A60BDC70-D98E-451D-96FF-09D09DC48E9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -144,10 +144,10 @@
     <t>Нижний Новгород</t>
   </si>
   <si>
+    <t>index</t>
+  </si>
+  <si>
     <t>city</t>
-  </si>
-  <si>
-    <t>index</t>
   </si>
 </sst>
 </file>
@@ -210,40 +210,27 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="1">
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-  </dxfs>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -522,16 +509,15 @@
   <dimension ref="A1:C48"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.140625" style="6"/>
     <col min="2" max="2" width="16.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" s="8" t="s">
+      <c r="A1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B1" t="s">
         <v>40</v>
-      </c>
-      <c r="B1" s="8" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
@@ -544,74 +530,74 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="4">
-        <v>0.5</v>
+        <v>1.2</v>
       </c>
       <c r="B3" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="4">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="B4" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="4">
-        <v>0.5</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="B5" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="4">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="B6" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="4">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="B7" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="4">
-        <v>0.75</v>
+        <v>0.9</v>
       </c>
       <c r="B8" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="4">
-        <v>1.1000000000000001</v>
+        <v>1</v>
       </c>
       <c r="B9" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="4">
-        <v>1</v>
+        <v>0.25</v>
       </c>
       <c r="B10" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="4">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="B11" t="s">
-        <v>20</v>
+        <v>38</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
@@ -619,111 +605,111 @@
         <v>0.9</v>
       </c>
       <c r="B12" t="s">
-        <v>4</v>
+        <v>23</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="4">
-        <v>1</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="B13" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="4">
-        <v>0.25</v>
+        <v>0.9</v>
       </c>
       <c r="B14" t="s">
-        <v>22</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="4">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="B15" t="s">
-        <v>38</v>
+        <v>3</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" s="4">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="B16" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="4">
-        <v>1.1000000000000001</v>
+        <v>1</v>
       </c>
       <c r="B17" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="4">
-        <v>0.9</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="B18" t="s">
-        <v>2</v>
+        <v>27</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" s="4">
-        <v>1</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="B19" t="s">
-        <v>3</v>
+        <v>28</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" s="4">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="B20" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" s="4">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="B21" t="s">
-        <v>26</v>
+        <v>12</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" s="4">
-        <v>1.1000000000000001</v>
+        <v>0.8</v>
       </c>
       <c r="B22" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" s="4">
-        <v>1.1000000000000001</v>
+        <v>1</v>
       </c>
       <c r="B23" t="s">
-        <v>28</v>
+        <v>16</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" s="4">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="B24" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" s="4">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="B25" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
@@ -731,7 +717,7 @@
         <v>1</v>
       </c>
       <c r="B26" t="s">
-        <v>31</v>
+        <v>13</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
@@ -739,15 +725,15 @@
         <v>1</v>
       </c>
       <c r="B27" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" s="4">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="B28" t="s">
-        <v>33</v>
+        <v>14</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
@@ -775,7 +761,7 @@
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A32" s="5">
+      <c r="A32" s="6">
         <v>1.2</v>
       </c>
       <c r="B32" s="3" t="s">
@@ -783,7 +769,7 @@
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A33" s="5">
+      <c r="A33" s="6">
         <v>1</v>
       </c>
       <c r="B33" s="3" t="s">
@@ -791,7 +777,7 @@
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A34" s="5">
+      <c r="A34" s="6">
         <v>1.2</v>
       </c>
       <c r="B34" s="3" t="s">
@@ -799,25 +785,23 @@
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A35" s="5">
+      <c r="A35" s="6">
         <v>1.2</v>
       </c>
       <c r="B35" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C35" s="1"/>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A36" s="5">
+      <c r="A36" s="6">
         <v>1.4</v>
       </c>
       <c r="B36" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C36" s="2"/>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A37" s="5">
+      <c r="A37" s="6">
         <v>1.2</v>
       </c>
       <c r="B37" s="3" t="s">
@@ -826,16 +810,16 @@
       <c r="C37" s="1"/>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A38" s="5">
+      <c r="A38" s="6">
         <v>1</v>
       </c>
       <c r="B38" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C38" s="1"/>
+      <c r="C38" s="2"/>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A39" s="5">
+      <c r="A39" s="6">
         <v>0.55000000000000004</v>
       </c>
       <c r="B39" s="3" t="s">
@@ -844,7 +828,7 @@
       <c r="C39" s="1"/>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A40" s="5">
+      <c r="A40" s="6">
         <v>0.45</v>
       </c>
       <c r="B40" s="3" t="s">
@@ -852,29 +836,45 @@
       </c>
       <c r="C40" s="1"/>
     </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A41" s="6"/>
+      <c r="B41" s="3"/>
+      <c r="C41" s="1"/>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A42" s="6"/>
+      <c r="B42" s="3"/>
+      <c r="C42" s="1"/>
+    </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A43" s="6"/>
+      <c r="B43" s="3"/>
       <c r="C43" s="1"/>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A44" s="6"/>
+      <c r="B44" s="3"/>
       <c r="C44" s="1"/>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A45" s="6"/>
+      <c r="B45" s="3"/>
       <c r="C45" s="1"/>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A46" s="6"/>
+      <c r="B46" s="3"/>
       <c r="C46" s="1"/>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A47" s="4"/>
+      <c r="A47" s="6"/>
+      <c r="B47" s="3"/>
       <c r="C47" s="1"/>
     </row>
     <row r="48" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A48" s="7"/>
+      <c r="A48" s="5"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="B46:B1048576 B1:B40">
-    <cfRule type="duplicateValues" dxfId="0" priority="3"/>
-  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>